--- a/docs/lem/files/xslope_eight_layers.xlsx
+++ b/docs/lem/files/xslope_eight_layers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/lem/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B712D58-131E-AF40-9057-1C724BA5F667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82A2D899-5785-F741-909D-9A696D234972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34040" yWindow="2680" windowWidth="34200" windowHeight="20240" activeTab="3" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="34040" yWindow="2680" windowWidth="34200" windowHeight="20240" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -955,7 +955,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1077,13 +1077,13 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1103,6 +1103,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9570,8 +9573,12 @@
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
+      <c r="W9" s="54">
+        <v>700000</v>
+      </c>
+      <c r="X9" s="17">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
@@ -9610,8 +9617,12 @@
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
+      <c r="W10" s="54">
+        <v>700000</v>
+      </c>
+      <c r="X10" s="17">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
@@ -9650,8 +9661,12 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
+      <c r="W11" s="54">
+        <v>700000</v>
+      </c>
+      <c r="X11" s="17">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
@@ -9690,8 +9705,12 @@
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
+      <c r="W12" s="54">
+        <v>700000</v>
+      </c>
+      <c r="X12" s="17">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
@@ -9730,8 +9749,12 @@
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
+      <c r="W13" s="54">
+        <v>700000</v>
+      </c>
+      <c r="X13" s="17">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
@@ -9770,8 +9793,12 @@
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
       <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
+      <c r="W14" s="54">
+        <v>700000</v>
+      </c>
+      <c r="X14" s="17">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
@@ -9810,8 +9837,12 @@
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
       <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
+      <c r="W15" s="54">
+        <v>700000</v>
+      </c>
+      <c r="X15" s="17">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
@@ -9850,8 +9881,12 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
+      <c r="W16" s="54">
+        <v>700000</v>
+      </c>
+      <c r="X16" s="17">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
@@ -10412,74 +10447,74 @@
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="D4" s="45" t="s">
+      <c r="B4" s="47"/>
+      <c r="D4" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="45"/>
-      <c r="G4" s="45" t="s">
+      <c r="E4" s="47"/>
+      <c r="G4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="45"/>
-      <c r="J4" s="45" t="s">
+      <c r="H4" s="47"/>
+      <c r="J4" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="45"/>
-      <c r="M4" s="45" t="s">
+      <c r="K4" s="47"/>
+      <c r="M4" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="45"/>
-      <c r="P4" s="45" t="s">
+      <c r="N4" s="47"/>
+      <c r="P4" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="45"/>
+      <c r="Q4" s="47"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="45" t="s">
+      <c r="S4" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="T4" s="45"/>
+      <c r="T4" s="47"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="45" t="s">
+      <c r="V4" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="W4" s="45"/>
+      <c r="W4" s="47"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="45" t="s">
+      <c r="Y4" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="45"/>
+      <c r="Z4" s="47"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="45" t="s">
+      <c r="AB4" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="AC4" s="45"/>
-      <c r="AE4" s="45" t="s">
+      <c r="AC4" s="47"/>
+      <c r="AE4" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="AF4" s="45"/>
+      <c r="AF4" s="47"/>
       <c r="AG4" s="1"/>
-      <c r="AH4" s="45" t="s">
+      <c r="AH4" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="AI4" s="45"/>
+      <c r="AI4" s="47"/>
       <c r="AJ4" s="1"/>
-      <c r="AK4" s="45" t="s">
+      <c r="AK4" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="AL4" s="45"/>
+      <c r="AL4" s="47"/>
       <c r="AM4" s="1"/>
-      <c r="AN4" s="45" t="s">
+      <c r="AN4" s="47" t="s">
         <v>119</v>
       </c>
-      <c r="AO4" s="45"/>
+      <c r="AO4" s="47"/>
       <c r="AP4" s="1"/>
-      <c r="AQ4" s="45" t="s">
+      <c r="AQ4" s="47" t="s">
         <v>120</v>
       </c>
-      <c r="AR4" s="45"/>
+      <c r="AR4" s="47"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="41" t="s">
@@ -10582,89 +10617,89 @@
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="46" t="str">
+      <c r="A6" s="45" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>soil 1</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="D6" s="46" t="str">
+      <c r="B6" s="46"/>
+      <c r="D6" s="45" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>soil 2</v>
       </c>
-      <c r="E6" s="47"/>
-      <c r="G6" s="46" t="str">
+      <c r="E6" s="46"/>
+      <c r="G6" s="45" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>soil 3</v>
       </c>
-      <c r="H6" s="47"/>
-      <c r="J6" s="46" t="str">
+      <c r="H6" s="46"/>
+      <c r="J6" s="45" t="str">
         <f>_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>soil 4</v>
       </c>
-      <c r="K6" s="47"/>
-      <c r="M6" s="46" t="str">
+      <c r="K6" s="46"/>
+      <c r="M6" s="45" t="str">
         <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>soil 5</v>
       </c>
-      <c r="N6" s="47"/>
-      <c r="P6" s="46" t="str">
+      <c r="N6" s="46"/>
+      <c r="P6" s="45" t="str">
         <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>soil 6</v>
       </c>
-      <c r="Q6" s="47"/>
+      <c r="Q6" s="46"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="46" t="str">
+      <c r="S6" s="45" t="str">
         <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>soil 7</v>
       </c>
-      <c r="T6" s="47"/>
+      <c r="T6" s="46"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="46" t="str">
+      <c r="V6" s="45" t="str">
         <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v>soil 8</v>
       </c>
-      <c r="W6" s="47"/>
+      <c r="W6" s="46"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="46" t="str">
+      <c r="Y6" s="45" t="str">
         <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="47"/>
+      <c r="Z6" s="46"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="46" t="str">
+      <c r="AB6" s="45" t="str">
         <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="47"/>
-      <c r="AE6" s="46" t="str">
+      <c r="AC6" s="46"/>
+      <c r="AE6" s="45" t="str">
         <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="47"/>
+      <c r="AF6" s="46"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="46" t="str">
+      <c r="AH6" s="45" t="str">
         <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="47"/>
+      <c r="AI6" s="46"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="46" t="str">
+      <c r="AK6" s="45" t="str">
         <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="47"/>
+      <c r="AL6" s="46"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="46" t="str">
+      <c r="AN6" s="45" t="str">
         <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="47"/>
+      <c r="AO6" s="46"/>
       <c r="AP6" s="1"/>
-      <c r="AQ6" s="46" t="str">
+      <c r="AQ6" s="45" t="str">
         <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="47"/>
+      <c r="AR6" s="46"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -11649,36 +11684,36 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AQ4:AR4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AB6:AC6"/>
     <mergeCell ref="AE6:AF6"/>
     <mergeCell ref="AH6:AI6"/>
     <mergeCell ref="AK6:AL6"/>
     <mergeCell ref="AN6:AO6"/>
     <mergeCell ref="AQ6:AR6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/lem/files/xslope_eight_layers.xlsx
+++ b/docs/lem/files/xslope_eight_layers.xlsx
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="163">
   <si>
     <t>X</t>
   </si>
@@ -645,6 +645,37 @@
   </si>
   <si>
     <t>soil 8</t>
+  </si>
+  <si>
+    <t>psi</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>psi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -8045,7 +8076,7 @@
         <v>79</v>
       </c>
       <c r="D5" s="35">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -9490,8 +9521,8 @@
       <c r="I8" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="J8" s="26" t="s">
-        <v>81</v>
+      <c r="J8" s="21" t="s">
+        <v>161</v>
       </c>
       <c r="K8" s="21" t="s">
         <v>88</v>
@@ -9512,7 +9543,7 @@
         <v>82</v>
       </c>
       <c r="Q8" s="23" t="s">
-        <v>83</v>
+        <v>162</v>
       </c>
       <c r="R8" s="25" t="s">
         <v>92</v>
@@ -10367,7 +10398,7 @@
     <mergeCell ref="R7:V7"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
-  <conditionalFormatting sqref="E9:F50">
+  <conditionalFormatting sqref="F9:F50">
     <cfRule type="expression" dxfId="8" priority="3">
       <formula>$D9="cp"</formula>
     </cfRule>
@@ -10382,7 +10413,7 @@
       <formula>$D9="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M9:N50">
+  <conditionalFormatting sqref="N9:N50">
     <cfRule type="expression" dxfId="5" priority="6">
       <formula>$D9="cp"</formula>
     </cfRule>

--- a/docs/lem/files/xslope_eight_layers.xlsx
+++ b/docs/lem/files/xslope_eight_layers.xlsx
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="318">
   <si>
     <t>XSLOPE Input Template</t>
   </si>
@@ -992,6 +992,167 @@
   </si>
   <si>
     <t>auto</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>g</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(c)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(c/p)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(d)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>s(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>psi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>g</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>sat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>q</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>p</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3243,7 +3404,7 @@
         <v>270</v>
       </c>
       <c r="H2" s="40" t="s">
-        <v>271</v>
+        <v>317</v>
       </c>
       <c r="I2" s="40" t="s">
         <v>253</v>
@@ -5722,7 +5883,7 @@
         <v>111</v>
       </c>
       <c r="D10" s="48" t="s">
-        <v>112</v>
+        <v>316</v>
       </c>
       <c r="E10" s="44" t="s">
         <v>113</v>
@@ -5791,22 +5952,22 @@
         <v>133</v>
       </c>
       <c r="AA10" s="46" t="s">
-        <v>134</v>
+        <v>311</v>
       </c>
       <c r="AB10" s="46" t="s">
-        <v>135</v>
+        <v>312</v>
       </c>
       <c r="AC10" s="47" t="s">
         <v>136</v>
       </c>
       <c r="AD10" s="46" t="s">
-        <v>137</v>
+        <v>313</v>
       </c>
       <c r="AE10" s="46" t="s">
-        <v>138</v>
+        <v>314</v>
       </c>
       <c r="AF10" s="47" t="s">
-        <v>139</v>
+        <v>315</v>
       </c>
       <c r="AG10" s="23" t="s">
         <v>140</v>

--- a/docs/lem/files/xslope_eight_layers.xlsx
+++ b/docs/lem/files/xslope_eight_layers.xlsx
@@ -6036,7 +6036,9 @@
       <c r="K11" s="3">
         <v>0.0</v>
       </c>
-      <c r="L11" s="3"/>
+      <c r="L11" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M11" s="3">
         <v>700000.0</v>
       </c>
@@ -6160,7 +6162,9 @@
       <c r="K12" s="3">
         <v>0.0</v>
       </c>
-      <c r="L12" s="3"/>
+      <c r="L12" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M12" s="3">
         <v>700000.0</v>
       </c>
@@ -6284,7 +6288,9 @@
       <c r="K13" s="3">
         <v>0.0</v>
       </c>
-      <c r="L13" s="3"/>
+      <c r="L13" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M13" s="3">
         <v>700000.0</v>
       </c>
@@ -6408,7 +6414,9 @@
       <c r="K14" s="3">
         <v>0.0</v>
       </c>
-      <c r="L14" s="3"/>
+      <c r="L14" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M14" s="3">
         <v>700000.0</v>
       </c>
@@ -6532,7 +6540,9 @@
       <c r="K15" s="3">
         <v>0.0</v>
       </c>
-      <c r="L15" s="3"/>
+      <c r="L15" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M15" s="3">
         <v>700000.0</v>
       </c>
@@ -6656,7 +6666,9 @@
       <c r="K16" s="3">
         <v>0.0</v>
       </c>
-      <c r="L16" s="3"/>
+      <c r="L16" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M16" s="3">
         <v>700000.0</v>
       </c>
@@ -6780,7 +6792,9 @@
       <c r="K17" s="3">
         <v>0.0</v>
       </c>
-      <c r="L17" s="3"/>
+      <c r="L17" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M17" s="3">
         <v>700000.0</v>
       </c>
@@ -6904,7 +6918,9 @@
       <c r="K18" s="3">
         <v>0.0</v>
       </c>
-      <c r="L18" s="3"/>
+      <c r="L18" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M18" s="3">
         <v>700000.0</v>
       </c>
